--- a/healthcare_surveys/030_healthcare_ethics_decision_making_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/030_healthcare_ethics_decision_making_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Section 1 - General Attitudes</t>
+          <t>General Attitudes</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Section 2 - Specific Scenarios</t>
+          <t>Challenging Situations</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Section 3 - Clinical Scenarios</t>
+          <t>Patient-Reported Outcomes</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Section 4 - Patient-Reported Outcomes</t>
+          <t>Handling Conflicts</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Section 5 - Clinician-Reported Outcomes</t>
+          <t>Decision-Making Process</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Section 6 - Team-Based Outcomes</t>
+          <t>Patient Education</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Section 7 - Team-Based Scenarios</t>
+          <t>Burnout and Compassion Fatigue</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Section 8 - Team-Based Scenarios</t>
+          <t>Technology Use</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,7 +722,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Section 9 - Team-Based Outcomes</t>
+          <t>Technology Use Examples</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Section 10 - Final Outcomes</t>
+          <t>Technology's Effectiveness</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thank you for participating</t>
+          <t>Difficult Decision</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Difficult Decision Examples</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,7 +814,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Biggest Concern</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Biggest Concern Examples</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Personal Values</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,7 +883,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Value Alignment</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,7 +906,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Decision-Making Priorities</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Priorities Examples</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,7 +952,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -962,11 +962,172 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Value-Based Decisions</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>page_21</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Value-Based Decisions Examples</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>page_22</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Final Thoughts</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>page_23</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>page_24</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Page 24</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>page_25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Page 25</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>page_26</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Page 26</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>page_27</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Page 27</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -983,12 +1144,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +1177,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>informed_consent_is_essential_in_patient_care.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Informed consent is essential in patient care.</t>
         </is>
       </c>
     </row>
@@ -1033,29 +1194,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>informed_consent_is_not_essential_in_patient_care.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Informed consent is not essential in patient care.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>page_3_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>a_patient_requesting_a_treatment_that_i_don't_recommend_but_is_requested_by_their_family_members.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>A patient requesting a treatment that I don't recommend but is requested by their family members.</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1228,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>a_healthcare_provider's_professional_opinion_is_not_in_line_with_my_own.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>A healthcare provider's professional opinion is not in line with my own.</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1245,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>a_colleague's_advice_influences_my_decision.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>A colleague's advice influences my decision.</t>
         </is>
       </c>
     </row>
@@ -1101,29 +1262,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>a_conflict_between_patient_care_and_administrative_priorities.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>A conflict between patient care and administrative priorities.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>page_3_choices</t>
+          <t>page_4_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>patient_wishes_are_not_aligned_with_my_own.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Patient wishes are not aligned with my own.</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1296,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>patient_cultural_values_are_not_aligned_with_my_own.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Patient cultural values are not aligned with my own.</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1313,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>patient_medical_condition_affects_my_own_well-being.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Patient medical condition affects my own well-being.</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1330,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>i_have_to_prioritize_one_patient_over_another.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>I have to prioritize one patient over another.</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1347,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>educate_and_empower_the_patient.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Educate and empower the patient.</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1364,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>seek_input_from_colleagues_or_superiors.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Seek input from colleagues or superiors.</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1381,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>involve_the_patient's_family_or_caregivers.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Involve the patient's family or caregivers.</t>
         </is>
       </c>
     </row>
@@ -1237,29 +1398,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>involve_other_healthcare_providers.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Involve other healthcare providers.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>page_6_choices</t>
+          <t>page_5_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>ignore_the_issue.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Ignore the issue.</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1432,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>rely_on_patient's_autonomy_and_self-determination.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Rely on patient's autonomy and self-determination.</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1449,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>rely_on_clinical_evidence_and_best_practices.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Rely on clinical evidence and best practices.</t>
         </is>
       </c>
     </row>
@@ -1305,46 +1466,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>rely_on_team-based_decision-making.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Rely on team-based decision-making.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>page_7_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>rely_on_personal_values_and_principles.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Rely on personal values and principles.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>page_7_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>rely_on_administrative_priorities.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Rely on administrative priorities.</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1517,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>provide_information_and_support.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Provide information and support.</t>
         </is>
       </c>
     </row>
@@ -1373,63 +1534,63 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>encourage_patient_involvement_in_the_decision-making_process.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Encourage patient involvement in the decision-making process.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>page_8_choices</t>
+          <t>page_7_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>involve_patients'_family_or_caregivers.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Involve patients' family or caregivers.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>page_8_choices</t>
+          <t>page_7_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>leave_decision-making_to_patients.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Leave decision-making to patients.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>page_8_choices</t>
+          <t>page_7_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>leave_decision-making_to_healthcare_providers.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Leave decision-making to healthcare providers.</t>
         </is>
       </c>
     </row>
@@ -1441,63 +1602,63 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>page_9_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>page_9_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>page_9_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1509,80 +1670,80 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>it's_an_essential_tool_for_patient_care.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>It's an essential tool for patient care.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>page_10_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>it's_a_useful_tool_for_patient_care.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>It's a useful tool for patient care.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>page_10_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>it's_a_potential_tool_for_patient_care.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>It's a potential tool for patient care.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>page_10_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>it's_not_relevant_to_patient_care.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>It's not relevant to patient care.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>page_10_choices</t>
+          <t>page_11_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>technology_is_an_effective_tool_for_supporting_patient_care.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Technology is an effective tool for supporting patient care.</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1755,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>technology_is_an_inefficient_tool_for_supporting_patient_care.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Technology is an inefficient tool for supporting patient care.</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1772,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>technology_is_a_necessary_evil_for_patient_care.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Technology is a necessary evil for patient care.</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1789,284 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>technology_is_not_necessary_for_patient_care.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Technology is not necessary for patient care.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>page_14_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>patient_safety_and_well-being.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Patient safety and well-being.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>page_14_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>clinical_outcomes.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Clinical outcomes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>page_14_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>team-based_collaboration.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Team-based collaboration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>page_14_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>administrative_priorities.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Administrative priorities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>page_17_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>patient_wishes_are_aligned_with_my_own.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Patient wishes are aligned with my own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>page_17_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>patient_cultural_values_are_aligned_with_my_own.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Patient cultural values are aligned with my own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>page_17_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>patient_medical_condition_does_not_affect_my_own_well-being.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Patient medical condition does not affect my own well-being.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>page_17_choices</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>i_do_not_have_to_prioritize_one_patient_over_another.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>I do not have to prioritize one patient over another.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>page_18_choices</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>patient_autonomy_and_self-determination.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Patient autonomy and self-determination.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>page_18_choices</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>clinical_evidence_and_best_practices.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Clinical evidence and best practices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>page_18_choices</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>team-based_decision-making.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Team-based decision-making.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>page_18_choices</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>administrative_priorities.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Administrative priorities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>page_20_choices</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>i_follow_my_personal_values_and_principles.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>I follow my personal values and principles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>page_20_choices</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>i_follow_my_employer's_policies.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>I follow my employer's policies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>page_20_choices</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>i_follow_my_colleagues'_advice.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>I follow my colleagues' advice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>page_20_choices</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>i_follow_administrative_priorities.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>I follow administrative priorities.</t>
         </is>
       </c>
     </row>
